--- a/数据表/Datas/ThreatLevelConfig_威胁等级配置.xlsx
+++ b/数据表/Datas/ThreatLevelConfig_威胁等级配置.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\Seek-Battle-Evacuate\数据表\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -81,7 +86,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>威胁等级</t>
@@ -90,7 +95,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>ID</t>
@@ -101,7 +106,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>显示名</t>
@@ -112,7 +117,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>最大正面视野距离，千分之一</t>
@@ -121,7 +126,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>Unity</t>
@@ -130,7 +135,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>单位</t>
@@ -141,7 +146,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>脱离视野后每秒降低警惕值</t>
@@ -152,7 +157,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>该段最大距离，单位千分之一</t>
@@ -161,7 +166,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>Unity</t>
@@ -170,7 +175,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>单位</t>
@@ -181,7 +186,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>每秒增加警惕值，满值</t>
@@ -190,7 +195,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>1000</t>
@@ -201,7 +206,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>低威胁</t>
@@ -212,7 +217,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>中威胁</t>
@@ -223,7 +228,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>高威胁</t>
@@ -248,37 +253,37 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF006100"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF1F4E78"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF595959"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF9C0006"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF202020"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
@@ -435,13 +440,13 @@
     <font>
       <sz val="12"/>
       <color rgb="FF9C0006"/>
-      <name val="PingFang SC Regular"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF202020"/>
-      <name val="PingFang SC Regular"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1567,17 +1572,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="6"/>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultColWidth="29.5833333333333" defaultRowHeight="20" customHeight="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="10" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.6764705882353" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10" style="2" customWidth="1"/>
-    <col min="4" max="4" width="26.7132352941176" style="2" customWidth="1"/>
-    <col min="5" max="5" width="30.1470588235294" style="2" customWidth="1"/>
-    <col min="6" max="6" width="38.9632352941176" style="2" customWidth="1"/>
-    <col min="7" max="7" width="29.4117647058824" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="12.8333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.8333333333333" style="2" customWidth="1"/>
+    <col min="3" max="3" width="9.91666666666667" style="2" customWidth="1"/>
+    <col min="4" max="4" width="39.9166666666667" style="2" customWidth="1"/>
+    <col min="5" max="5" width="29.5833333333333" style="2" customWidth="1"/>
+    <col min="6" max="6" width="40.1666666666667" style="2" customWidth="1"/>
+    <col min="7" max="7" width="32.4166666666667" style="2" customWidth="1"/>
+    <col min="8" max="16383" width="29.5833333333333" style="1" customWidth="1"/>
+    <col min="16384" max="16384" width="29.5833333333333" style="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:7">
@@ -1692,7 +1698,7 @@
         <v>22</v>
       </c>
       <c r="D6" s="16">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="E6" s="16">
         <v>200</v>
@@ -1701,7 +1707,7 @@
         <v>1000</v>
       </c>
       <c r="G6" s="16">
-        <v>600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:7">
@@ -1711,10 +1717,10 @@
       <c r="D7" s="16"/>
       <c r="E7" s="16"/>
       <c r="F7" s="16">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="G7" s="16">
-        <v>300</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:7">
@@ -1724,10 +1730,10 @@
       <c r="D8" s="16"/>
       <c r="E8" s="16"/>
       <c r="F8" s="16">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="G8" s="16">
-        <v>150</v>
+        <v>600</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:7">
@@ -1757,7 +1763,7 @@
         <v>1500</v>
       </c>
       <c r="G10" s="16">
-        <v>800</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:7">
@@ -1770,7 +1776,7 @@
         <v>3000</v>
       </c>
       <c r="G11" s="16">
-        <v>400</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:7">
@@ -1783,7 +1789,7 @@
         <v>5000</v>
       </c>
       <c r="G12" s="16">
-        <v>200</v>
+        <v>800</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:7">
@@ -1810,10 +1816,10 @@
         <v>100</v>
       </c>
       <c r="F14" s="16">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G14" s="16">
-        <v>1000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:7">
@@ -1823,10 +1829,10 @@
       <c r="D15" s="16"/>
       <c r="E15" s="16"/>
       <c r="F15" s="16">
+        <v>2000</v>
+      </c>
+      <c r="G15" s="16">
         <v>4000</v>
-      </c>
-      <c r="G15" s="16">
-        <v>500</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:7">
@@ -1836,10 +1842,23 @@
       <c r="D16" s="16"/>
       <c r="E16" s="16"/>
       <c r="F16" s="16">
+        <v>4000</v>
+      </c>
+      <c r="G16" s="16">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:7">
+      <c r="A17" s="16"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16">
         <v>7000</v>
       </c>
-      <c r="G16" s="16">
-        <v>250</v>
+      <c r="G17" s="16">
+        <v>800</v>
       </c>
     </row>
   </sheetData>

--- a/数据表/Datas/ThreatLevelConfig_威胁等级配置.xlsx
+++ b/数据表/Datas/ThreatLevelConfig_威胁等级配置.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
@@ -40,9 +40,6 @@
     <t>id</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>maxViewDistanceMilli</t>
   </si>
   <si>
@@ -56,9 +53,6 @@
   </si>
   <si>
     <t>EnemyPartyThreatLevel</t>
-  </si>
-  <si>
-    <t>string</t>
   </si>
   <si>
     <t>int</t>
@@ -99,17 +93,6 @@
         <charset val="134"/>
       </rPr>
       <t>ID</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9C0006"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>显示名</t>
     </r>
   </si>
   <si>
@@ -209,7 +192,7 @@
         <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
-      <t>低威胁</t>
+      <t>低</t>
     </r>
   </si>
   <si>
@@ -220,7 +203,7 @@
         <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
-      <t>中威胁</t>
+      <t>中</t>
     </r>
   </si>
   <si>
@@ -231,7 +214,7 @@
         <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
-      <t>高威胁</t>
+      <t>高</t>
     </r>
   </si>
 </sst>
@@ -439,13 +422,13 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF202020"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF202020"/>
+      <color rgb="FF9C0006"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1572,21 +1555,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="29.5833333333333" defaultRowHeight="20" customHeight="1" outlineLevelCol="6"/>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultColWidth="29.5833333333333" defaultRowHeight="20" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12.8333333333333" style="1" customWidth="1"/>
     <col min="2" max="2" width="24.8333333333333" style="2" customWidth="1"/>
-    <col min="3" max="3" width="9.91666666666667" style="2" customWidth="1"/>
-    <col min="4" max="4" width="39.9166666666667" style="2" customWidth="1"/>
-    <col min="5" max="5" width="29.5833333333333" style="2" customWidth="1"/>
-    <col min="6" max="6" width="40.1666666666667" style="2" customWidth="1"/>
-    <col min="7" max="7" width="32.4166666666667" style="2" customWidth="1"/>
-    <col min="8" max="16383" width="29.5833333333333" style="1" customWidth="1"/>
-    <col min="16384" max="16384" width="29.5833333333333" style="1"/>
+    <col min="3" max="3" width="39.9166666666667" style="2" customWidth="1"/>
+    <col min="4" max="4" width="29.5833333333333" style="2" customWidth="1"/>
+    <col min="5" max="5" width="40.1666666666667" style="2" customWidth="1"/>
+    <col min="6" max="6" width="32.4166666666667" style="2" customWidth="1"/>
+    <col min="7" max="16382" width="29.5833333333333" style="1" customWidth="1"/>
+    <col min="16383" max="16384" width="29.5833333333333" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:7">
+    <row r="1" customHeight="1" spans="1:6">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1599,272 +1581,241 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6"/>
+    </row>
+    <row r="2" customHeight="1" spans="1:6">
+      <c r="A2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6"/>
+      <c r="B2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="10"/>
     </row>
-    <row r="2" customHeight="1" spans="1:7">
-      <c r="A2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="8" t="s">
+    <row r="3" customHeight="1" spans="1:6">
+      <c r="A3" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="9" t="s">
+      <c r="B3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="10"/>
+      <c r="C3" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" customHeight="1" spans="1:7">
-      <c r="A3" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:7">
+    <row r="4" customHeight="1" spans="1:6">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
+      <c r="E4" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="F4" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:6">
+      <c r="A5" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="B5" s="15" t="s">
         <v>14</v>
       </c>
+      <c r="C5" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="5" customHeight="1" spans="1:7">
-      <c r="A5" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="15" t="s">
+    <row r="6" customHeight="1" spans="1:6">
+      <c r="A6" s="16"/>
+      <c r="B6" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>21</v>
+      <c r="C6" s="16">
+        <v>3500</v>
+      </c>
+      <c r="D6" s="16">
+        <v>200</v>
+      </c>
+      <c r="E6" s="16">
+        <v>1000</v>
+      </c>
+      <c r="F6" s="16">
+        <v>2000</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:7">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16">
-        <v>1</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="16">
-        <v>3500</v>
-      </c>
-      <c r="E6" s="16">
-        <v>200</v>
-      </c>
-      <c r="F6" s="16">
-        <v>1000</v>
-      </c>
-      <c r="G6" s="16">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:7">
+    <row r="7" customHeight="1" spans="1:6">
       <c r="A7" s="16"/>
       <c r="B7" s="16"/>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
+      <c r="E7" s="16">
+        <v>2200</v>
+      </c>
       <c r="F7" s="16">
-        <v>2200</v>
-      </c>
-      <c r="G7" s="16">
         <v>1200</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:7">
+    <row r="8" customHeight="1" spans="1:6">
       <c r="A8" s="16"/>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
       <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
+      <c r="E8" s="16">
+        <v>3500</v>
+      </c>
       <c r="F8" s="16">
-        <v>3500</v>
-      </c>
-      <c r="G8" s="16">
         <v>600</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:7">
+    <row r="9" customHeight="1" spans="1:6">
       <c r="A9" s="16"/>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
     </row>
-    <row r="10" customHeight="1" spans="1:7">
+    <row r="10" customHeight="1" spans="1:6">
       <c r="A10" s="16"/>
-      <c r="B10" s="16">
-        <v>2</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>23</v>
+      <c r="B10" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="16">
+        <v>5000</v>
       </c>
       <c r="D10" s="16">
-        <v>5000</v>
+        <v>150</v>
       </c>
       <c r="E10" s="16">
-        <v>150</v>
+        <v>1500</v>
       </c>
       <c r="F10" s="16">
-        <v>1500</v>
-      </c>
-      <c r="G10" s="16">
         <v>1800</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:7">
+    <row r="11" customHeight="1" spans="1:6">
       <c r="A11" s="16"/>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
       <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
+      <c r="E11" s="16">
+        <v>3000</v>
+      </c>
       <c r="F11" s="16">
-        <v>3000</v>
-      </c>
-      <c r="G11" s="16">
         <v>1000</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:7">
+    <row r="12" customHeight="1" spans="1:6">
       <c r="A12" s="16"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
       <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
+      <c r="E12" s="16">
+        <v>5000</v>
+      </c>
       <c r="F12" s="16">
-        <v>5000</v>
-      </c>
-      <c r="G12" s="16">
         <v>800</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:7">
+    <row r="13" customHeight="1" spans="1:6">
       <c r="A13" s="16"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
       <c r="E13" s="16"/>
       <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
     </row>
-    <row r="14" customHeight="1" spans="1:7">
+    <row r="14" customHeight="1" spans="1:6">
       <c r="A14" s="16"/>
-      <c r="B14" s="16">
-        <v>3</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>24</v>
+      <c r="B14" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="16">
+        <v>7000</v>
       </c>
       <c r="D14" s="16">
-        <v>7000</v>
+        <v>100</v>
       </c>
       <c r="E14" s="16">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="F14" s="16">
-        <v>1000</v>
-      </c>
-      <c r="G14" s="16">
         <v>8000</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:7">
+    <row r="15" customHeight="1" spans="1:6">
       <c r="A15" s="16"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
+      <c r="E15" s="16">
+        <v>2000</v>
+      </c>
       <c r="F15" s="16">
-        <v>2000</v>
-      </c>
-      <c r="G15" s="16">
         <v>4000</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:7">
+    <row r="16" customHeight="1" spans="1:6">
       <c r="A16" s="16"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
       <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
+      <c r="E16" s="16">
+        <v>4000</v>
+      </c>
       <c r="F16" s="16">
-        <v>4000</v>
-      </c>
-      <c r="G16" s="16">
         <v>1000</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:7">
+    <row r="17" customHeight="1" spans="1:6">
       <c r="A17" s="16"/>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
       <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
+      <c r="E17" s="16">
+        <v>7000</v>
+      </c>
       <c r="F17" s="16">
-        <v>7000</v>
-      </c>
-      <c r="G17" s="16">
         <v>800</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="E2:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
